--- a/assets/sample_薪资模板_广州_电商运营助理.xlsx
+++ b/assets/sample_薪资模板_广州_电商运营助理.xlsx
@@ -24,7 +24,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="6">
+  <fonts count="4">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -40,23 +40,13 @@
     </font>
     <font>
       <name val="Arial"/>
-      <color rgb="000000FF"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <color rgb="00000000"/>
+      <color rgb="001F4E78"/>
       <sz val="10"/>
     </font>
     <font>
       <name val="Arial"/>
       <b val="1"/>
       <sz val="14"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <color rgb="00008000"/>
-      <sz val="10"/>
     </font>
   </fonts>
   <fills count="3">
@@ -90,7 +80,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -101,29 +91,14 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="9" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="9" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="9" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -879,110 +854,110 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="4" t="n">
+      <c r="A4" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="B4" s="5" t="inlineStr">
+      <c r="B4" s="3" t="inlineStr">
         <is>
           <t>绩效工资</t>
         </is>
       </c>
-      <c r="C4" s="5" t="inlineStr">
+      <c r="C4" s="3" t="inlineStr">
         <is>
           <t>浮动薪资</t>
         </is>
       </c>
-      <c r="D4" s="4" t="n">
+      <c r="D4" s="2" t="n">
         <v>2000</v>
       </c>
-      <c r="E4" s="4" t="n">
+      <c r="E4" s="2" t="n">
         <v>1200</v>
       </c>
-      <c r="F4" s="4" t="n">
+      <c r="F4" s="2" t="n">
         <v>2000</v>
       </c>
-      <c r="G4" s="4" t="n">
+      <c r="G4" s="2" t="n">
         <v>3000</v>
       </c>
-      <c r="H4" s="5" t="inlineStr">
+      <c r="H4" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="I4" s="5" t="inlineStr">
+      <c r="I4" s="3" t="inlineStr">
         <is>
           <t>绩效考核得分</t>
         </is>
       </c>
-      <c r="J4" s="5" t="inlineStr">
+      <c r="J4" s="3" t="inlineStr">
         <is>
           <t>绩效得分/100*标准</t>
         </is>
       </c>
-      <c r="K4" s="5" t="inlineStr">
+      <c r="K4" s="3" t="inlineStr">
         <is>
           <t>月度</t>
         </is>
       </c>
-      <c r="L4" s="5" t="inlineStr">
+      <c r="L4" s="3" t="inlineStr">
         <is>
           <t>与KPI挂钩</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="4" t="n">
+      <c r="A5" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="B5" s="5" t="inlineStr">
+      <c r="B5" s="3" t="inlineStr">
         <is>
           <t>加班工资</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr">
+      <c r="C5" s="3" t="inlineStr">
         <is>
           <t>浮动薪资</t>
         </is>
       </c>
-      <c r="D5" s="4" t="n">
+      <c r="D5" s="2" t="n">
         <v>650</v>
       </c>
-      <c r="E5" s="5" t="inlineStr">
+      <c r="E5" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F5" s="5" t="inlineStr">
+      <c r="F5" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G5" s="5" t="inlineStr">
+      <c r="G5" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="H5" s="5" t="inlineStr">
+      <c r="H5" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="I5" s="5" t="inlineStr">
+      <c r="I5" s="3" t="inlineStr">
         <is>
           <t>实际加班时长</t>
         </is>
       </c>
-      <c r="J5" s="5" t="inlineStr">
+      <c r="J5" s="3" t="inlineStr">
         <is>
           <t>按劳动法1.5/2/3倍</t>
         </is>
       </c>
-      <c r="K5" s="5" t="inlineStr">
+      <c r="K5" s="3" t="inlineStr">
         <is>
           <t>月度</t>
         </is>
       </c>
-      <c r="L5" s="5" t="inlineStr">
+      <c r="L5" s="3" t="inlineStr">
         <is>
           <t>以基本工资为基数</t>
         </is>
@@ -1221,236 +1196,236 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="4" t="n">
+      <c r="A10" s="2" t="n">
         <v>9</v>
       </c>
-      <c r="B10" s="5" t="inlineStr">
+      <c r="B10" s="3" t="inlineStr">
         <is>
           <t>五险一金(个人)</t>
         </is>
       </c>
-      <c r="C10" s="5" t="inlineStr">
+      <c r="C10" s="3" t="inlineStr">
         <is>
           <t>代扣项</t>
         </is>
       </c>
-      <c r="D10" s="4">
+      <c r="D10" s="2">
         <f>'计算示例'!B20</f>
         <v/>
       </c>
-      <c r="E10" s="5" t="inlineStr">
+      <c r="E10" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F10" s="5" t="inlineStr">
+      <c r="F10" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G10" s="5" t="inlineStr">
+      <c r="G10" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="H10" s="5" t="inlineStr">
+      <c r="H10" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="I10" s="5" t="inlineStr">
+      <c r="I10" s="3" t="inlineStr">
         <is>
           <t>缴费基数*比例</t>
         </is>
       </c>
-      <c r="J10" s="5" t="inlineStr">
+      <c r="J10" s="3" t="inlineStr">
         <is>
           <t>养老8%+医疗2%+失业0.5%+公积金</t>
         </is>
       </c>
-      <c r="K10" s="5" t="inlineStr">
+      <c r="K10" s="3" t="inlineStr">
         <is>
           <t>月度</t>
         </is>
       </c>
-      <c r="L10" s="5" t="inlineStr">
+      <c r="L10" s="3" t="inlineStr">
         <is>
           <t>单位另承担约30%</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="4" t="n">
+      <c r="A11" s="2" t="n">
         <v>10</v>
       </c>
-      <c r="B11" s="5" t="inlineStr">
+      <c r="B11" s="3" t="inlineStr">
         <is>
           <t>个人所得税</t>
         </is>
       </c>
-      <c r="C11" s="5" t="inlineStr">
+      <c r="C11" s="3" t="inlineStr">
         <is>
           <t>代扣项</t>
         </is>
       </c>
-      <c r="D11" s="4">
+      <c r="D11" s="2">
         <f>'计算示例'!B23</f>
         <v/>
       </c>
-      <c r="E11" s="5" t="inlineStr">
+      <c r="E11" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F11" s="5" t="inlineStr">
+      <c r="F11" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G11" s="5" t="inlineStr">
+      <c r="G11" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="H11" s="5" t="inlineStr">
+      <c r="H11" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="I11" s="5" t="inlineStr">
+      <c r="I11" s="3" t="inlineStr">
         <is>
           <t>应纳税所得额</t>
         </is>
       </c>
-      <c r="J11" s="5" t="inlineStr">
+      <c r="J11" s="3" t="inlineStr">
         <is>
           <t>累计预扣法</t>
         </is>
       </c>
-      <c r="K11" s="5" t="inlineStr">
+      <c r="K11" s="3" t="inlineStr">
         <is>
           <t>月度</t>
         </is>
       </c>
-      <c r="L11" s="5" t="inlineStr">
+      <c r="L11" s="3" t="inlineStr">
         <is>
           <t>按个税法计算</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="4" t="n">
+      <c r="A12" s="2" t="n">
         <v>11</v>
       </c>
-      <c r="B12" s="5" t="inlineStr">
+      <c r="B12" s="3" t="inlineStr">
         <is>
           <t>应发工资</t>
         </is>
       </c>
-      <c r="C12" s="5" t="inlineStr">
+      <c r="C12" s="3" t="inlineStr">
         <is>
           <t>汇总</t>
         </is>
       </c>
-      <c r="D12" s="4">
+      <c r="D12" s="2">
         <f>'计算示例'!B19</f>
         <v/>
       </c>
-      <c r="E12" s="5" t="inlineStr">
+      <c r="E12" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F12" s="5" t="inlineStr">
+      <c r="F12" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G12" s="5" t="inlineStr">
+      <c r="G12" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="H12" s="5" t="inlineStr">
+      <c r="H12" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="I12" s="5" t="inlineStr">
+      <c r="I12" s="3" t="inlineStr">
         <is>
           <t>固定+浮动+补贴</t>
         </is>
       </c>
-      <c r="J12" s="5" t="inlineStr">
+      <c r="J12" s="3" t="inlineStr">
         <is>
           <t>SUM(固定+浮动+补贴)</t>
         </is>
       </c>
-      <c r="K12" s="5" t="inlineStr">
+      <c r="K12" s="3" t="inlineStr">
         <is>
           <t>月度</t>
         </is>
       </c>
-      <c r="L12" s="5" t="inlineStr">
+      <c r="L12" s="3" t="inlineStr">
         <is>
           <t>税前总薪资</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="4" t="n">
+      <c r="A13" s="2" t="n">
         <v>12</v>
       </c>
-      <c r="B13" s="5" t="inlineStr">
+      <c r="B13" s="3" t="inlineStr">
         <is>
           <t>实发工资</t>
         </is>
       </c>
-      <c r="C13" s="5" t="inlineStr">
+      <c r="C13" s="3" t="inlineStr">
         <is>
           <t>汇总</t>
         </is>
       </c>
-      <c r="D13" s="4">
+      <c r="D13" s="2">
         <f>'计算示例'!B24</f>
         <v/>
       </c>
-      <c r="E13" s="5" t="inlineStr">
+      <c r="E13" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F13" s="5" t="inlineStr">
+      <c r="F13" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G13" s="5" t="inlineStr">
+      <c r="G13" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="H13" s="5" t="inlineStr">
+      <c r="H13" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="I13" s="5" t="inlineStr">
+      <c r="I13" s="3" t="inlineStr">
         <is>
           <t>应发-代扣项</t>
         </is>
       </c>
-      <c r="J13" s="5" t="inlineStr">
+      <c r="J13" s="3" t="inlineStr">
         <is>
           <t>应发-五险一金-个税</t>
         </is>
       </c>
-      <c r="K13" s="5" t="inlineStr">
+      <c r="K13" s="3" t="inlineStr">
         <is>
           <t>月度</t>
         </is>
       </c>
-      <c r="L13" s="5" t="inlineStr">
+      <c r="L13" s="3" t="inlineStr">
         <is>
           <t>到手金额</t>
         </is>
@@ -1467,7 +1442,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I9"/>
+  <dimension ref="A1:I7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1534,7 +1509,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>销售额达成率</t>
+          <t>销售额/GMV 达成率</t>
         </is>
       </c>
       <c r="C2" s="3" t="inlineStr">
@@ -1544,7 +1519,7 @@
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>销售额达成实际/目标</t>
+          <t>销售额/GMV 达成实际/目标</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
@@ -1574,315 +1549,225 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="4" t="n">
+      <c r="A3" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="B3" s="5" t="inlineStr">
-        <is>
-          <t>订单处理效率</t>
-        </is>
-      </c>
-      <c r="C3" s="5" t="inlineStr">
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>用户增长/活跃度</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>20%</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>用户增长/活跃度</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>&gt;=90分</t>
+        </is>
+      </c>
+      <c r="F3" s="3" t="inlineStr">
+        <is>
+          <t>达标100分；每低1分扣2-5分</t>
+        </is>
+      </c>
+      <c r="G3" s="3" t="inlineStr">
+        <is>
+          <t>业务系统/主管评分</t>
+        </is>
+      </c>
+      <c r="H3" s="3" t="inlineStr">
+        <is>
+          <t>月度</t>
+        </is>
+      </c>
+      <c r="I3" s="3" t="inlineStr">
+        <is>
+          <t>核心指标</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>活动执行完成率</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
         <is>
           <t>15%</t>
         </is>
       </c>
-      <c r="D3" s="5" t="inlineStr">
-        <is>
-          <t>订单处理效实际/目标</t>
-        </is>
-      </c>
-      <c r="E3" s="5" t="inlineStr">
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>活动执行完成实际/目标</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
         <is>
           <t>&gt;=85分</t>
         </is>
       </c>
-      <c r="F3" s="5" t="inlineStr">
+      <c r="F4" s="3" t="inlineStr">
         <is>
           <t>达标100分；每低1分扣2-5分</t>
         </is>
       </c>
-      <c r="G3" s="5" t="inlineStr">
+      <c r="G4" s="3" t="inlineStr">
         <is>
           <t>业务系统/主管评分</t>
         </is>
       </c>
-      <c r="H3" s="5" t="inlineStr">
+      <c r="H4" s="3" t="inlineStr">
         <is>
           <t>月度</t>
         </is>
       </c>
-      <c r="I3" s="5" t="inlineStr">
+      <c r="I4" s="3" t="inlineStr">
         <is>
           <t>辅助指标</t>
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="B4" s="5" t="inlineStr">
-        <is>
-          <t>客户满意度</t>
-        </is>
-      </c>
-      <c r="C4" s="5" t="inlineStr">
+    <row r="5">
+      <c r="A5" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>内容/商品质量</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
         <is>
           <t>15%</t>
         </is>
       </c>
-      <c r="D4" s="5" t="inlineStr">
-        <is>
-          <t>客户满意度</t>
-        </is>
-      </c>
-      <c r="E4" s="5" t="inlineStr">
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>内容/商品质量</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="inlineStr">
         <is>
           <t>&gt;=85分</t>
         </is>
       </c>
-      <c r="F4" s="5" t="inlineStr">
+      <c r="F5" s="3" t="inlineStr">
         <is>
           <t>达标100分；每低1分扣2-5分</t>
         </is>
       </c>
-      <c r="G4" s="5" t="inlineStr">
+      <c r="G5" s="3" t="inlineStr">
         <is>
           <t>业务系统/主管评分</t>
         </is>
       </c>
-      <c r="H4" s="5" t="inlineStr">
+      <c r="H5" s="3" t="inlineStr">
         <is>
           <t>月度</t>
         </is>
       </c>
-      <c r="I4" s="5" t="inlineStr">
+      <c r="I5" s="3" t="inlineStr">
         <is>
           <t>辅助指标</t>
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="B5" s="5" t="inlineStr">
-        <is>
-          <t>库存准确率</t>
-        </is>
-      </c>
-      <c r="C5" s="5" t="inlineStr">
+    <row r="6">
+      <c r="A6" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>数据分析准确率</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>15%</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>数据分析准确实际/目标</t>
+        </is>
+      </c>
+      <c r="E6" s="3" t="inlineStr">
+        <is>
+          <t>&gt;=85分</t>
+        </is>
+      </c>
+      <c r="F6" s="3" t="inlineStr">
+        <is>
+          <t>达标100分；每低1分扣2-5分</t>
+        </is>
+      </c>
+      <c r="G6" s="3" t="inlineStr">
+        <is>
+          <t>业务系统/主管评分</t>
+        </is>
+      </c>
+      <c r="H6" s="3" t="inlineStr">
+        <is>
+          <t>月度</t>
+        </is>
+      </c>
+      <c r="I6" s="3" t="inlineStr">
+        <is>
+          <t>辅助指标</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>渠道拓展与维护</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="inlineStr">
         <is>
           <t>10%</t>
         </is>
       </c>
-      <c r="D5" s="5" t="inlineStr">
-        <is>
-          <t>库存准确实际/目标</t>
-        </is>
-      </c>
-      <c r="E5" s="5" t="inlineStr">
+      <c r="D7" s="3" t="inlineStr">
+        <is>
+          <t>渠道拓展与维护</t>
+        </is>
+      </c>
+      <c r="E7" s="3" t="inlineStr">
         <is>
           <t>&gt;=85分</t>
         </is>
       </c>
-      <c r="F5" s="5" t="inlineStr">
+      <c r="F7" s="3" t="inlineStr">
         <is>
           <t>达标100分；每低1分扣2-5分</t>
         </is>
       </c>
-      <c r="G5" s="5" t="inlineStr">
+      <c r="G7" s="3" t="inlineStr">
         <is>
           <t>业务系统/主管评分</t>
         </is>
       </c>
-      <c r="H5" s="5" t="inlineStr">
+      <c r="H7" s="3" t="inlineStr">
         <is>
           <t>月度</t>
         </is>
       </c>
-      <c r="I5" s="5" t="inlineStr">
-        <is>
-          <t>辅助指标</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="B6" s="5" t="inlineStr">
-        <is>
-          <t>活动执行完成率</t>
-        </is>
-      </c>
-      <c r="C6" s="5" t="inlineStr">
-        <is>
-          <t>10%</t>
-        </is>
-      </c>
-      <c r="D6" s="5" t="inlineStr">
-        <is>
-          <t>活动执行完成实际/目标</t>
-        </is>
-      </c>
-      <c r="E6" s="5" t="inlineStr">
-        <is>
-          <t>&gt;=85分</t>
-        </is>
-      </c>
-      <c r="F6" s="5" t="inlineStr">
-        <is>
-          <t>达标100分；每低1分扣2-5分</t>
-        </is>
-      </c>
-      <c r="G6" s="5" t="inlineStr">
-        <is>
-          <t>业务系统/主管评分</t>
-        </is>
-      </c>
-      <c r="H6" s="5" t="inlineStr">
-        <is>
-          <t>月度</t>
-        </is>
-      </c>
-      <c r="I6" s="5" t="inlineStr">
-        <is>
-          <t>辅助指标</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="4" t="n">
-        <v>6</v>
-      </c>
-      <c r="B7" s="5" t="inlineStr">
-        <is>
-          <t>数据报表准确率</t>
-        </is>
-      </c>
-      <c r="C7" s="5" t="inlineStr">
-        <is>
-          <t>10%</t>
-        </is>
-      </c>
-      <c r="D7" s="5" t="inlineStr">
-        <is>
-          <t>数据报表准确实际/目标</t>
-        </is>
-      </c>
-      <c r="E7" s="5" t="inlineStr">
-        <is>
-          <t>&gt;=85分</t>
-        </is>
-      </c>
-      <c r="F7" s="5" t="inlineStr">
-        <is>
-          <t>达标100分；每低1分扣2-5分</t>
-        </is>
-      </c>
-      <c r="G7" s="5" t="inlineStr">
-        <is>
-          <t>业务系统/主管评分</t>
-        </is>
-      </c>
-      <c r="H7" s="5" t="inlineStr">
-        <is>
-          <t>月度</t>
-        </is>
-      </c>
-      <c r="I7" s="5" t="inlineStr">
-        <is>
-          <t>辅助指标</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="4" t="n">
-        <v>7</v>
-      </c>
-      <c r="B8" s="5" t="inlineStr">
-        <is>
-          <t>工作态度与协作</t>
-        </is>
-      </c>
-      <c r="C8" s="5" t="inlineStr">
-        <is>
-          <t>10%</t>
-        </is>
-      </c>
-      <c r="D8" s="5" t="inlineStr">
-        <is>
-          <t>工作态度与协作</t>
-        </is>
-      </c>
-      <c r="E8" s="5" t="inlineStr">
-        <is>
-          <t>&gt;=85分</t>
-        </is>
-      </c>
-      <c r="F8" s="5" t="inlineStr">
-        <is>
-          <t>达标100分；每低1分扣2-5分</t>
-        </is>
-      </c>
-      <c r="G8" s="5" t="inlineStr">
-        <is>
-          <t>业务系统/主管评分</t>
-        </is>
-      </c>
-      <c r="H8" s="5" t="inlineStr">
-        <is>
-          <t>月度</t>
-        </is>
-      </c>
-      <c r="I8" s="5" t="inlineStr">
-        <is>
-          <t>辅助指标</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="B9" s="5" t="inlineStr">
-        <is>
-          <t>学习成长</t>
-        </is>
-      </c>
-      <c r="C9" s="5" t="inlineStr">
-        <is>
-          <t>5%</t>
-        </is>
-      </c>
-      <c r="D9" s="5" t="inlineStr">
-        <is>
-          <t>学习成长</t>
-        </is>
-      </c>
-      <c r="E9" s="5" t="inlineStr">
-        <is>
-          <t>&gt;=85分</t>
-        </is>
-      </c>
-      <c r="F9" s="5" t="inlineStr">
-        <is>
-          <t>达标100分；每低1分扣2-5分</t>
-        </is>
-      </c>
-      <c r="G9" s="5" t="inlineStr">
-        <is>
-          <t>业务系统/主管评分</t>
-        </is>
-      </c>
-      <c r="H9" s="5" t="inlineStr">
-        <is>
-          <t>月度</t>
-        </is>
-      </c>
-      <c r="I9" s="5" t="inlineStr">
+      <c r="I7" s="3" t="inlineStr">
         <is>
           <t>辅助指标</t>
         </is>
@@ -1949,245 +1834,245 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="4" t="n">
+      <c r="A2" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="B2" s="5" t="inlineStr">
+      <c r="B2" s="3" t="inlineStr">
         <is>
           <t>试用期转正调薪</t>
         </is>
       </c>
-      <c r="C2" s="5" t="inlineStr">
+      <c r="C2" s="3" t="inlineStr">
         <is>
           <t>试用期考核通过</t>
         </is>
       </c>
-      <c r="D2" s="5" t="inlineStr">
+      <c r="D2" s="3" t="inlineStr">
         <is>
           <t>0-10%</t>
         </is>
       </c>
-      <c r="E2" s="5" t="inlineStr">
+      <c r="E2" s="3" t="inlineStr">
         <is>
           <t>转正次月</t>
         </is>
       </c>
-      <c r="F2" s="5" t="inlineStr">
+      <c r="F2" s="3" t="inlineStr">
         <is>
           <t>部门主管→HR→总经理</t>
         </is>
       </c>
-      <c r="G2" s="5" t="inlineStr">
+      <c r="G2" s="3" t="inlineStr">
         <is>
           <t>根据试用期表现定档</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="4" t="n">
+      <c r="A3" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="B3" s="5" t="inlineStr">
+      <c r="B3" s="3" t="inlineStr">
         <is>
           <t>年度普调</t>
         </is>
       </c>
-      <c r="C3" s="5" t="inlineStr">
+      <c r="C3" s="3" t="inlineStr">
         <is>
           <t>入职满1年且年度绩效≥B</t>
         </is>
       </c>
-      <c r="D3" s="5" t="inlineStr">
+      <c r="D3" s="3" t="inlineStr">
         <is>
           <t>3-8%</t>
         </is>
       </c>
-      <c r="E3" s="5" t="inlineStr">
+      <c r="E3" s="3" t="inlineStr">
         <is>
           <t>次年1月</t>
         </is>
       </c>
-      <c r="F3" s="5" t="inlineStr">
+      <c r="F3" s="3" t="inlineStr">
         <is>
           <t>HR提案→管理层审批</t>
         </is>
       </c>
-      <c r="G3" s="5" t="inlineStr">
+      <c r="G3" s="3" t="inlineStr">
         <is>
           <t>参考市场薪酬涨幅</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="4" t="n">
+      <c r="A4" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="B4" s="5" t="inlineStr">
+      <c r="B4" s="3" t="inlineStr">
         <is>
           <t>晋升调薪</t>
         </is>
       </c>
-      <c r="C4" s="5" t="inlineStr">
+      <c r="C4" s="3" t="inlineStr">
         <is>
           <t>职级晋升</t>
         </is>
       </c>
-      <c r="D4" s="5" t="inlineStr">
+      <c r="D4" s="3" t="inlineStr">
         <is>
           <t>10-25%</t>
         </is>
       </c>
-      <c r="E4" s="5" t="inlineStr">
+      <c r="E4" s="3" t="inlineStr">
         <is>
           <t>晋升次月</t>
         </is>
       </c>
-      <c r="F4" s="5" t="inlineStr">
+      <c r="F4" s="3" t="inlineStr">
         <is>
           <t>部门提名→晋升评审→总经理</t>
         </is>
       </c>
-      <c r="G4" s="5" t="inlineStr">
+      <c r="G4" s="3" t="inlineStr">
         <is>
           <t>每晋升1级至少10%</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="4" t="n">
+      <c r="A5" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="B5" s="5" t="inlineStr">
+      <c r="B5" s="3" t="inlineStr">
         <is>
           <t>绩效调薪</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr">
+      <c r="C5" s="3" t="inlineStr">
         <is>
           <t>连续2个季度绩效A或年度绩效A</t>
         </is>
       </c>
-      <c r="D5" s="5" t="inlineStr">
+      <c r="D5" s="3" t="inlineStr">
         <is>
           <t>5-15%</t>
         </is>
       </c>
-      <c r="E5" s="5" t="inlineStr">
+      <c r="E5" s="3" t="inlineStr">
         <is>
           <t>绩效评定次月</t>
         </is>
       </c>
-      <c r="F5" s="5" t="inlineStr">
+      <c r="F5" s="3" t="inlineStr">
         <is>
           <t>主管申请→HR审核→总经理</t>
         </is>
       </c>
-      <c r="G5" s="5" t="inlineStr">
+      <c r="G5" s="3" t="inlineStr">
         <is>
           <t>不与晋升调薪重复享受</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="4" t="n">
+      <c r="A6" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="B6" s="5" t="inlineStr">
+      <c r="B6" s="3" t="inlineStr">
         <is>
           <t>市场薪酬调整</t>
         </is>
       </c>
-      <c r="C6" s="5" t="inlineStr">
+      <c r="C6" s="3" t="inlineStr">
         <is>
           <t>岗位市场薪酬显著变化</t>
         </is>
       </c>
-      <c r="D6" s="5" t="inlineStr">
+      <c r="D6" s="3" t="inlineStr">
         <is>
           <t>5-10%</t>
         </is>
       </c>
-      <c r="E6" s="5" t="inlineStr">
+      <c r="E6" s="3" t="inlineStr">
         <is>
           <t>调整方案确认次月</t>
         </is>
       </c>
-      <c r="F6" s="5" t="inlineStr">
+      <c r="F6" s="3" t="inlineStr">
         <is>
           <t>HR调研→管理层审批</t>
         </is>
       </c>
-      <c r="G6" s="5" t="inlineStr">
+      <c r="G6" s="3" t="inlineStr">
         <is>
           <t>需有薪酬调研数据支撑</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="4" t="n">
+      <c r="A7" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="B7" s="5" t="inlineStr">
+      <c r="B7" s="3" t="inlineStr">
         <is>
           <t>特殊贡献调薪</t>
         </is>
       </c>
-      <c r="C7" s="5" t="inlineStr">
+      <c r="C7" s="3" t="inlineStr">
         <is>
           <t>重大项目突破/特殊贡献</t>
         </is>
       </c>
-      <c r="D7" s="5" t="inlineStr">
+      <c r="D7" s="3" t="inlineStr">
         <is>
           <t>10-30%</t>
         </is>
       </c>
-      <c r="E7" s="5" t="inlineStr">
+      <c r="E7" s="3" t="inlineStr">
         <is>
           <t>贡献确认次月</t>
         </is>
       </c>
-      <c r="F7" s="5" t="inlineStr">
+      <c r="F7" s="3" t="inlineStr">
         <is>
           <t>部门申请→总经理特批</t>
         </is>
       </c>
-      <c r="G7" s="5" t="inlineStr">
+      <c r="G7" s="3" t="inlineStr">
         <is>
           <t>一事一议</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="4" t="n">
+      <c r="A8" s="2" t="n">
         <v>7</v>
       </c>
-      <c r="B8" s="5" t="inlineStr">
+      <c r="B8" s="3" t="inlineStr">
         <is>
           <t>留任调薪</t>
         </is>
       </c>
-      <c r="C8" s="5" t="inlineStr">
+      <c r="C8" s="3" t="inlineStr">
         <is>
           <t>核心人才面临外部高薪挖角</t>
         </is>
       </c>
-      <c r="D8" s="5" t="inlineStr">
+      <c r="D8" s="3" t="inlineStr">
         <is>
           <t>10-20%</t>
         </is>
       </c>
-      <c r="E8" s="5" t="inlineStr">
+      <c r="E8" s="3" t="inlineStr">
         <is>
           <t>审批通过后次月</t>
         </is>
       </c>
-      <c r="F8" s="5" t="inlineStr">
+      <c r="F8" s="3" t="inlineStr">
         <is>
           <t>HR评估→总经理审批</t>
         </is>
       </c>
-      <c r="G8" s="5" t="inlineStr">
+      <c r="G8" s="3" t="inlineStr">
         <is>
           <t>需签订服务期协议</t>
         </is>
@@ -2266,360 +2151,360 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="4" t="n">
+      <c r="A2" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="B2" s="5" t="inlineStr">
+      <c r="B2" s="3" t="inlineStr">
         <is>
           <t>月度销售提成</t>
         </is>
       </c>
-      <c r="C2" s="5" t="inlineStr">
-        <is>
-          <t>电商运营助理</t>
-        </is>
-      </c>
-      <c r="D2" s="5" t="inlineStr">
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>互联网电商运营助理</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
         <is>
           <t>个人负责销售额</t>
         </is>
       </c>
-      <c r="E2" s="5" t="inlineStr">
+      <c r="E2" s="3" t="inlineStr">
         <is>
           <t>0.3%-0.8%</t>
         </is>
       </c>
-      <c r="F2" s="5" t="inlineStr">
+      <c r="F2" s="3" t="inlineStr">
         <is>
           <t>月度</t>
         </is>
       </c>
-      <c r="G2" s="5" t="inlineStr">
+      <c r="G2" s="3" t="inlineStr">
         <is>
           <t>销售额达标且回款完成</t>
         </is>
       </c>
-      <c r="H2" s="5" t="inlineStr">
+      <c r="H2" s="3" t="inlineStr">
         <is>
           <t>销售额*提成比例</t>
         </is>
       </c>
-      <c r="I2" s="5" t="inlineStr">
+      <c r="I2" s="3" t="inlineStr">
         <is>
           <t>阶梯提成</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="4" t="n">
+      <c r="A3" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="B3" s="5" t="inlineStr">
+      <c r="B3" s="3" t="inlineStr">
         <is>
           <t>月度绩效奖金</t>
         </is>
       </c>
-      <c r="C3" s="5" t="inlineStr">
-        <is>
-          <t>电商运营助理</t>
-        </is>
-      </c>
-      <c r="D3" s="5" t="inlineStr">
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>互联网电商运营助理</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
         <is>
           <t>绩效标准金额</t>
         </is>
       </c>
-      <c r="E3" s="5" t="inlineStr">
+      <c r="E3" s="3" t="inlineStr">
         <is>
           <t>0-120%</t>
         </is>
       </c>
-      <c r="F3" s="5" t="inlineStr">
+      <c r="F3" s="3" t="inlineStr">
         <is>
           <t>月度</t>
         </is>
       </c>
-      <c r="G3" s="5" t="inlineStr">
+      <c r="G3" s="3" t="inlineStr">
         <is>
           <t>月度绩效得分≥60</t>
         </is>
       </c>
-      <c r="H3" s="5" t="inlineStr">
+      <c r="H3" s="3" t="inlineStr">
         <is>
           <t>绩效标准*绩效系数</t>
         </is>
       </c>
-      <c r="I3" s="5" t="inlineStr">
+      <c r="I3" s="3" t="inlineStr">
         <is>
           <t>与绩效考核表挂钩</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="4" t="n">
+      <c r="A4" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="B4" s="5" t="inlineStr">
+      <c r="B4" s="3" t="inlineStr">
         <is>
           <t>季度奖金</t>
         </is>
       </c>
-      <c r="C4" s="5" t="inlineStr">
-        <is>
-          <t>电商运营助理</t>
-        </is>
-      </c>
-      <c r="D4" s="5" t="inlineStr">
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>互联网电商运营助理</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
         <is>
           <t>月基本工资</t>
         </is>
       </c>
-      <c r="E4" s="5" t="inlineStr">
+      <c r="E4" s="3" t="inlineStr">
         <is>
           <t>0.5-1.0个月</t>
         </is>
       </c>
-      <c r="F4" s="5" t="inlineStr">
+      <c r="F4" s="3" t="inlineStr">
         <is>
           <t>季度</t>
         </is>
       </c>
-      <c r="G4" s="5" t="inlineStr">
+      <c r="G4" s="3" t="inlineStr">
         <is>
           <t>季度目标达成</t>
         </is>
       </c>
-      <c r="H4" s="5" t="inlineStr">
+      <c r="H4" s="3" t="inlineStr">
         <is>
           <t>基本工资*0.8</t>
         </is>
       </c>
-      <c r="I4" s="5" t="inlineStr">
+      <c r="I4" s="3" t="inlineStr">
         <is>
           <t>每季度评估</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="4" t="n">
+      <c r="A5" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="B5" s="5" t="inlineStr">
+      <c r="B5" s="3" t="inlineStr">
         <is>
           <t>年度奖金</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr">
-        <is>
-          <t>电商运营助理</t>
-        </is>
-      </c>
-      <c r="D5" s="5" t="inlineStr">
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>互联网电商运营助理</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
         <is>
           <t>月基本工资</t>
         </is>
       </c>
-      <c r="E5" s="5" t="inlineStr">
+      <c r="E5" s="3" t="inlineStr">
         <is>
           <t>1.0-2.0个月</t>
         </is>
       </c>
-      <c r="F5" s="5" t="inlineStr">
+      <c r="F5" s="3" t="inlineStr">
         <is>
           <t>年度</t>
         </is>
       </c>
-      <c r="G5" s="5" t="inlineStr">
+      <c r="G5" s="3" t="inlineStr">
         <is>
           <t>年度绩效≥B且在职</t>
         </is>
       </c>
-      <c r="H5" s="5" t="inlineStr">
+      <c r="H5" s="3" t="inlineStr">
         <is>
           <t>基本工资*1.5</t>
         </is>
       </c>
-      <c r="I5" s="5" t="inlineStr">
+      <c r="I5" s="3" t="inlineStr">
         <is>
           <t>春节前发放</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="4" t="n">
+      <c r="A6" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="B6" s="5" t="inlineStr">
+      <c r="B6" s="3" t="inlineStr">
         <is>
           <t>项目奖金</t>
         </is>
       </c>
-      <c r="C6" s="5" t="inlineStr">
-        <is>
-          <t>电商运营助理</t>
-        </is>
-      </c>
-      <c r="D6" s="5" t="inlineStr">
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>互联网电商运营助理</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="inlineStr">
         <is>
           <t>项目利润</t>
         </is>
       </c>
-      <c r="E6" s="5" t="inlineStr">
+      <c r="E6" s="3" t="inlineStr">
         <is>
           <t>5%-15%</t>
         </is>
       </c>
-      <c r="F6" s="5" t="inlineStr">
+      <c r="F6" s="3" t="inlineStr">
         <is>
           <t>项目结束</t>
         </is>
       </c>
-      <c r="G6" s="5" t="inlineStr">
+      <c r="G6" s="3" t="inlineStr">
         <is>
           <t>项目验收通过</t>
         </is>
       </c>
-      <c r="H6" s="5" t="inlineStr">
+      <c r="H6" s="3" t="inlineStr">
         <is>
           <t>项目利润*分配比例</t>
         </is>
       </c>
-      <c r="I6" s="5" t="inlineStr">
+      <c r="I6" s="3" t="inlineStr">
         <is>
           <t>专项激励</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="4" t="n">
+      <c r="A7" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="B7" s="5" t="inlineStr">
+      <c r="B7" s="3" t="inlineStr">
         <is>
           <t>全勤奖</t>
         </is>
       </c>
-      <c r="C7" s="5" t="inlineStr">
+      <c r="C7" s="3" t="inlineStr">
         <is>
           <t>全员</t>
         </is>
       </c>
-      <c r="D7" s="5" t="inlineStr">
+      <c r="D7" s="3" t="inlineStr">
         <is>
           <t>固定金额</t>
         </is>
       </c>
-      <c r="E7" s="5" t="inlineStr">
+      <c r="E7" s="3" t="inlineStr">
         <is>
           <t>260元</t>
         </is>
       </c>
-      <c r="F7" s="5" t="inlineStr">
+      <c r="F7" s="3" t="inlineStr">
         <is>
           <t>月度</t>
         </is>
       </c>
-      <c r="G7" s="5" t="inlineStr">
+      <c r="G7" s="3" t="inlineStr">
         <is>
           <t>当月无缺勤迟到早退</t>
         </is>
       </c>
-      <c r="H7" s="5" t="inlineStr">
+      <c r="H7" s="3" t="inlineStr">
         <is>
           <t>固定260元</t>
         </is>
       </c>
-      <c r="I7" s="5" t="inlineStr">
+      <c r="I7" s="3" t="inlineStr">
         <is>
           <t>超3次取消</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="4" t="n">
+      <c r="A8" s="2" t="n">
         <v>7</v>
       </c>
-      <c r="B8" s="5" t="inlineStr">
+      <c r="B8" s="3" t="inlineStr">
         <is>
           <t>伯乐奖</t>
         </is>
       </c>
-      <c r="C8" s="5" t="inlineStr">
+      <c r="C8" s="3" t="inlineStr">
         <is>
           <t>全员</t>
         </is>
       </c>
-      <c r="D8" s="5" t="inlineStr">
+      <c r="D8" s="3" t="inlineStr">
         <is>
           <t>固定金额</t>
         </is>
       </c>
-      <c r="E8" s="5" t="inlineStr">
+      <c r="E8" s="3" t="inlineStr">
         <is>
           <t>500-2000元</t>
         </is>
       </c>
-      <c r="F8" s="5" t="inlineStr">
+      <c r="F8" s="3" t="inlineStr">
         <is>
           <t>实时</t>
         </is>
       </c>
-      <c r="G8" s="5" t="inlineStr">
+      <c r="G8" s="3" t="inlineStr">
         <is>
           <t>推荐人才成功转正</t>
         </is>
       </c>
-      <c r="H8" s="5" t="inlineStr">
+      <c r="H8" s="3" t="inlineStr">
         <is>
           <t>按岗位级别定</t>
         </is>
       </c>
-      <c r="I8" s="5" t="inlineStr">
+      <c r="I8" s="3" t="inlineStr">
         <is>
           <t>转正后发放</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="4" t="n">
+      <c r="A9" s="2" t="n">
         <v>8</v>
       </c>
-      <c r="B9" s="5" t="inlineStr">
+      <c r="B9" s="3" t="inlineStr">
         <is>
           <t>年终分红</t>
         </is>
       </c>
-      <c r="C9" s="5" t="inlineStr">
+      <c r="C9" s="3" t="inlineStr">
         <is>
           <t>核心员工</t>
         </is>
       </c>
-      <c r="D9" s="5" t="inlineStr">
+      <c r="D9" s="3" t="inlineStr">
         <is>
           <t>公司年度利润</t>
         </is>
       </c>
-      <c r="E9" s="5" t="inlineStr">
+      <c r="E9" s="3" t="inlineStr">
         <is>
           <t>0.5%-2%</t>
         </is>
       </c>
-      <c r="F9" s="5" t="inlineStr">
+      <c r="F9" s="3" t="inlineStr">
         <is>
           <t>年度</t>
         </is>
       </c>
-      <c r="G9" s="5" t="inlineStr">
+      <c r="G9" s="3" t="inlineStr">
         <is>
           <t>入职满1年且绩效≥B</t>
         </is>
       </c>
-      <c r="H9" s="5" t="inlineStr">
+      <c r="H9" s="3" t="inlineStr">
         <is>
           <t>利润池*个人分配比例</t>
         </is>
       </c>
-      <c r="I9" s="5" t="inlineStr">
+      <c r="I9" s="3" t="inlineStr">
         <is>
           <t>仅限资深员工</t>
         </is>
@@ -2686,595 +2571,595 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="4" t="n">
+      <c r="A2" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="B2" s="5" t="inlineStr">
+      <c r="B2" s="3" t="inlineStr">
         <is>
           <t>养老保险</t>
         </is>
       </c>
-      <c r="C2" s="5" t="inlineStr">
+      <c r="C2" s="3" t="inlineStr">
         <is>
           <t>法定福利</t>
         </is>
       </c>
-      <c r="D2" s="5" t="inlineStr">
+      <c r="D2" s="3" t="inlineStr">
         <is>
           <t>基数*16%(单位)+8%(个人)</t>
         </is>
       </c>
-      <c r="E2" s="5" t="inlineStr">
+      <c r="E2" s="3" t="inlineStr">
         <is>
           <t>签订劳动合同</t>
         </is>
       </c>
-      <c r="F2" s="5" t="inlineStr">
+      <c r="F2" s="3" t="inlineStr">
         <is>
           <t>社保代缴</t>
         </is>
       </c>
-      <c r="G2" s="5" t="inlineStr">
+      <c r="G2" s="3" t="inlineStr">
         <is>
           <t>按当地社保政策</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="4" t="n">
+      <c r="A3" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="B3" s="5" t="inlineStr">
+      <c r="B3" s="3" t="inlineStr">
         <is>
           <t>医疗保险</t>
         </is>
       </c>
-      <c r="C3" s="5" t="inlineStr">
+      <c r="C3" s="3" t="inlineStr">
         <is>
           <t>法定福利</t>
         </is>
       </c>
-      <c r="D3" s="5" t="inlineStr">
+      <c r="D3" s="3" t="inlineStr">
         <is>
           <t>基数*8%(单位)+2%(个人)</t>
         </is>
       </c>
-      <c r="E3" s="5" t="inlineStr">
+      <c r="E3" s="3" t="inlineStr">
         <is>
           <t>签订劳动合同</t>
         </is>
       </c>
-      <c r="F3" s="5" t="inlineStr">
+      <c r="F3" s="3" t="inlineStr">
         <is>
           <t>社保代缴</t>
         </is>
       </c>
-      <c r="G3" s="5" t="inlineStr">
+      <c r="G3" s="3" t="inlineStr">
         <is>
           <t>含生育保险</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="4" t="n">
+      <c r="A4" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="B4" s="5" t="inlineStr">
+      <c r="B4" s="3" t="inlineStr">
         <is>
           <t>失业保险</t>
         </is>
       </c>
-      <c r="C4" s="5" t="inlineStr">
+      <c r="C4" s="3" t="inlineStr">
         <is>
           <t>法定福利</t>
         </is>
       </c>
-      <c r="D4" s="5" t="inlineStr">
+      <c r="D4" s="3" t="inlineStr">
         <is>
           <t>基数*0.5%(单位)+0.5%(个人)</t>
         </is>
       </c>
-      <c r="E4" s="5" t="inlineStr">
+      <c r="E4" s="3" t="inlineStr">
         <is>
           <t>签订劳动合同</t>
         </is>
       </c>
-      <c r="F4" s="5" t="inlineStr">
+      <c r="F4" s="3" t="inlineStr">
         <is>
           <t>社保代缴</t>
         </is>
       </c>
-      <c r="G4" s="5" t="inlineStr">
+      <c r="G4" s="3" t="inlineStr">
         <is>
           <t>按当地政策</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="4" t="n">
+      <c r="A5" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="B5" s="5" t="inlineStr">
+      <c r="B5" s="3" t="inlineStr">
         <is>
           <t>工伤保险</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr">
+      <c r="C5" s="3" t="inlineStr">
         <is>
           <t>法定福利</t>
         </is>
       </c>
-      <c r="D5" s="5" t="inlineStr">
+      <c r="D5" s="3" t="inlineStr">
         <is>
           <t>基数*0.2%-1.4%(单位)</t>
         </is>
       </c>
-      <c r="E5" s="5" t="inlineStr">
+      <c r="E5" s="3" t="inlineStr">
         <is>
           <t>签订劳动合同</t>
         </is>
       </c>
-      <c r="F5" s="5" t="inlineStr">
+      <c r="F5" s="3" t="inlineStr">
         <is>
           <t>社保代缴</t>
         </is>
       </c>
-      <c r="G5" s="5" t="inlineStr">
+      <c r="G5" s="3" t="inlineStr">
         <is>
           <t>按行业风险等级</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="4" t="n">
+      <c r="A6" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="B6" s="5" t="inlineStr">
+      <c r="B6" s="3" t="inlineStr">
         <is>
           <t>住房公积金</t>
         </is>
       </c>
-      <c r="C6" s="5" t="inlineStr">
+      <c r="C6" s="3" t="inlineStr">
         <is>
           <t>法定福利</t>
         </is>
       </c>
-      <c r="D6" s="5" t="inlineStr">
+      <c r="D6" s="3" t="inlineStr">
         <is>
           <t>基数*5%-12%(双边)</t>
         </is>
       </c>
-      <c r="E6" s="5" t="inlineStr">
+      <c r="E6" s="3" t="inlineStr">
         <is>
           <t>签订劳动合同</t>
         </is>
       </c>
-      <c r="F6" s="5" t="inlineStr">
+      <c r="F6" s="3" t="inlineStr">
         <is>
           <t>公积金代缴</t>
         </is>
       </c>
-      <c r="G6" s="5" t="inlineStr">
+      <c r="G6" s="3" t="inlineStr">
         <is>
           <t>单位和个人同比例</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="4" t="n">
+      <c r="A7" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="B7" s="5" t="inlineStr">
+      <c r="B7" s="3" t="inlineStr">
         <is>
           <t>补充医疗保险</t>
         </is>
       </c>
-      <c r="C7" s="5" t="inlineStr">
+      <c r="C7" s="3" t="inlineStr">
         <is>
           <t>补充福利</t>
         </is>
       </c>
-      <c r="D7" s="5" t="inlineStr">
+      <c r="D7" s="3" t="inlineStr">
         <is>
           <t>约200元/人/年</t>
         </is>
       </c>
-      <c r="E7" s="5" t="inlineStr">
+      <c r="E7" s="3" t="inlineStr">
         <is>
           <t>转正后</t>
         </is>
       </c>
-      <c r="F7" s="5" t="inlineStr">
+      <c r="F7" s="3" t="inlineStr">
         <is>
           <t>商业保险</t>
         </is>
       </c>
-      <c r="G7" s="5" t="inlineStr">
+      <c r="G7" s="3" t="inlineStr">
         <is>
           <t>覆盖门诊住院</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="4" t="n">
+      <c r="A8" s="2" t="n">
         <v>7</v>
       </c>
-      <c r="B8" s="5" t="inlineStr">
+      <c r="B8" s="3" t="inlineStr">
         <is>
           <t>带薪年假</t>
         </is>
       </c>
-      <c r="C8" s="5" t="inlineStr">
+      <c r="C8" s="3" t="inlineStr">
         <is>
           <t>法定福利</t>
         </is>
       </c>
-      <c r="D8" s="5" t="inlineStr">
+      <c r="D8" s="3" t="inlineStr">
         <is>
           <t>5-15天/年</t>
         </is>
       </c>
-      <c r="E8" s="5" t="inlineStr">
+      <c r="E8" s="3" t="inlineStr">
         <is>
           <t>入职满1年</t>
         </is>
       </c>
-      <c r="F8" s="5" t="inlineStr">
+      <c r="F8" s="3" t="inlineStr">
         <is>
           <t>申请休假</t>
         </is>
       </c>
-      <c r="G8" s="5" t="inlineStr">
+      <c r="G8" s="3" t="inlineStr">
         <is>
           <t>按工龄递增</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="4" t="n">
+      <c r="A9" s="2" t="n">
         <v>8</v>
       </c>
-      <c r="B9" s="5" t="inlineStr">
+      <c r="B9" s="3" t="inlineStr">
         <is>
           <t>法定节假日</t>
         </is>
       </c>
-      <c r="C9" s="5" t="inlineStr">
+      <c r="C9" s="3" t="inlineStr">
         <is>
           <t>法定福利</t>
         </is>
       </c>
-      <c r="D9" s="5" t="inlineStr">
+      <c r="D9" s="3" t="inlineStr">
         <is>
           <t>11天/年</t>
         </is>
       </c>
-      <c r="E9" s="5" t="inlineStr">
+      <c r="E9" s="3" t="inlineStr">
         <is>
           <t>全员</t>
         </is>
       </c>
-      <c r="F9" s="5" t="inlineStr">
+      <c r="F9" s="3" t="inlineStr">
         <is>
           <t>带薪休假</t>
         </is>
       </c>
-      <c r="G9" s="5" t="inlineStr">
+      <c r="G9" s="3" t="inlineStr">
         <is>
           <t>按国家规定</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="4" t="n">
+      <c r="A10" s="2" t="n">
         <v>9</v>
       </c>
-      <c r="B10" s="5" t="inlineStr">
+      <c r="B10" s="3" t="inlineStr">
         <is>
           <t>节日福利</t>
         </is>
       </c>
-      <c r="C10" s="5" t="inlineStr">
+      <c r="C10" s="3" t="inlineStr">
         <is>
           <t>补充福利</t>
         </is>
       </c>
-      <c r="D10" s="5" t="inlineStr">
+      <c r="D10" s="3" t="inlineStr">
         <is>
           <t>300-500元/节</t>
         </is>
       </c>
-      <c r="E10" s="5" t="inlineStr">
+      <c r="E10" s="3" t="inlineStr">
         <is>
           <t>全员</t>
         </is>
       </c>
-      <c r="F10" s="5" t="inlineStr">
+      <c r="F10" s="3" t="inlineStr">
         <is>
           <t>实物/购物卡/现金</t>
         </is>
       </c>
-      <c r="G10" s="5" t="inlineStr">
+      <c r="G10" s="3" t="inlineStr">
         <is>
           <t>春节/中秋/端午</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="4" t="n">
+      <c r="A11" s="2" t="n">
         <v>10</v>
       </c>
-      <c r="B11" s="5" t="inlineStr">
+      <c r="B11" s="3" t="inlineStr">
         <is>
           <t>生日福利</t>
         </is>
       </c>
-      <c r="C11" s="5" t="inlineStr">
+      <c r="C11" s="3" t="inlineStr">
         <is>
           <t>补充福利</t>
         </is>
       </c>
-      <c r="D11" s="5" t="inlineStr">
+      <c r="D11" s="3" t="inlineStr">
         <is>
           <t>200元礼品/礼金</t>
         </is>
       </c>
-      <c r="E11" s="5" t="inlineStr">
+      <c r="E11" s="3" t="inlineStr">
         <is>
           <t>全员</t>
         </is>
       </c>
-      <c r="F11" s="5" t="inlineStr">
+      <c r="F11" s="3" t="inlineStr">
         <is>
           <t>生日当月发放</t>
         </is>
       </c>
-      <c r="G11" s="5" t="inlineStr">
+      <c r="G11" s="3" t="inlineStr">
         <is>
           <t>或生日蛋糕券</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="4" t="n">
+      <c r="A12" s="2" t="n">
         <v>11</v>
       </c>
-      <c r="B12" s="5" t="inlineStr">
+      <c r="B12" s="3" t="inlineStr">
         <is>
           <t>培训补贴</t>
         </is>
       </c>
-      <c r="C12" s="5" t="inlineStr">
+      <c r="C12" s="3" t="inlineStr">
         <is>
           <t>补充福利</t>
         </is>
       </c>
-      <c r="D12" s="5" t="inlineStr">
+      <c r="D12" s="3" t="inlineStr">
         <is>
           <t>1000-3000元/年</t>
         </is>
       </c>
-      <c r="E12" s="5" t="inlineStr">
+      <c r="E12" s="3" t="inlineStr">
         <is>
           <t>年度培训计划内</t>
         </is>
       </c>
-      <c r="F12" s="5" t="inlineStr">
+      <c r="F12" s="3" t="inlineStr">
         <is>
           <t>报销/直付</t>
         </is>
       </c>
-      <c r="G12" s="5" t="inlineStr">
+      <c r="G12" s="3" t="inlineStr">
         <is>
           <t>外部课程/考证</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="4" t="n">
+      <c r="A13" s="2" t="n">
         <v>12</v>
       </c>
-      <c r="B13" s="5" t="inlineStr">
+      <c r="B13" s="3" t="inlineStr">
         <is>
           <t>团建经费</t>
         </is>
       </c>
-      <c r="C13" s="5" t="inlineStr">
+      <c r="C13" s="3" t="inlineStr">
         <is>
           <t>补充福利</t>
         </is>
       </c>
-      <c r="D13" s="5" t="inlineStr">
+      <c r="D13" s="3" t="inlineStr">
         <is>
           <t>100-200元/人/月</t>
         </is>
       </c>
-      <c r="E13" s="5" t="inlineStr">
+      <c r="E13" s="3" t="inlineStr">
         <is>
           <t>全员</t>
         </is>
       </c>
-      <c r="F13" s="5" t="inlineStr">
+      <c r="F13" s="3" t="inlineStr">
         <is>
           <t>部门统筹</t>
         </is>
       </c>
-      <c r="G13" s="5" t="inlineStr">
+      <c r="G13" s="3" t="inlineStr">
         <is>
           <t>季度或月度活动</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="4" t="n">
+      <c r="A14" s="2" t="n">
         <v>13</v>
       </c>
-      <c r="B14" s="5" t="inlineStr">
+      <c r="B14" s="3" t="inlineStr">
         <is>
           <t>下午茶</t>
         </is>
       </c>
-      <c r="C14" s="5" t="inlineStr">
+      <c r="C14" s="3" t="inlineStr">
         <is>
           <t>补充福利</t>
         </is>
       </c>
-      <c r="D14" s="5" t="inlineStr">
+      <c r="D14" s="3" t="inlineStr">
         <is>
           <t>约20元/人/周</t>
         </is>
       </c>
-      <c r="E14" s="5" t="inlineStr">
+      <c r="E14" s="3" t="inlineStr">
         <is>
           <t>全员</t>
         </is>
       </c>
-      <c r="F14" s="5" t="inlineStr">
+      <c r="F14" s="3" t="inlineStr">
         <is>
           <t>行政采购</t>
         </is>
       </c>
-      <c r="G14" s="5" t="inlineStr">
+      <c r="G14" s="3" t="inlineStr">
         <is>
           <t>每周固定</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="4" t="n">
+      <c r="A15" s="2" t="n">
         <v>14</v>
       </c>
-      <c r="B15" s="5" t="inlineStr">
+      <c r="B15" s="3" t="inlineStr">
         <is>
           <t>年度体检</t>
         </is>
       </c>
-      <c r="C15" s="5" t="inlineStr">
+      <c r="C15" s="3" t="inlineStr">
         <is>
           <t>补充福利</t>
         </is>
       </c>
-      <c r="D15" s="5" t="inlineStr">
+      <c r="D15" s="3" t="inlineStr">
         <is>
           <t>500-1000元/人</t>
         </is>
       </c>
-      <c r="E15" s="5" t="inlineStr">
+      <c r="E15" s="3" t="inlineStr">
         <is>
           <t>入职满1年</t>
         </is>
       </c>
-      <c r="F15" s="5" t="inlineStr">
+      <c r="F15" s="3" t="inlineStr">
         <is>
           <t>合作医院</t>
         </is>
       </c>
-      <c r="G15" s="5" t="inlineStr">
+      <c r="G15" s="3" t="inlineStr">
         <is>
           <t>每年1次</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="4" t="n">
+      <c r="A16" s="2" t="n">
         <v>15</v>
       </c>
-      <c r="B16" s="5" t="inlineStr">
+      <c r="B16" s="3" t="inlineStr">
         <is>
           <t>交通补助</t>
         </is>
       </c>
-      <c r="C16" s="5" t="inlineStr">
+      <c r="C16" s="3" t="inlineStr">
         <is>
           <t>津贴补贴</t>
         </is>
       </c>
-      <c r="D16" s="5" t="inlineStr">
+      <c r="D16" s="3" t="inlineStr">
         <is>
           <t>260元/月</t>
         </is>
       </c>
-      <c r="E16" s="5" t="inlineStr">
+      <c r="E16" s="3" t="inlineStr">
         <is>
           <t>外勤较多岗位</t>
         </is>
       </c>
-      <c r="F16" s="5" t="inlineStr">
+      <c r="F16" s="3" t="inlineStr">
         <is>
           <t>随工资发放</t>
         </is>
       </c>
-      <c r="G16" s="5" t="inlineStr">
+      <c r="G16" s="3" t="inlineStr">
         <is>
           <t>需提交外出记录</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="4" t="n">
+      <c r="A17" s="2" t="n">
         <v>16</v>
       </c>
-      <c r="B17" s="5" t="inlineStr">
+      <c r="B17" s="3" t="inlineStr">
         <is>
           <t>餐补</t>
         </is>
       </c>
-      <c r="C17" s="5" t="inlineStr">
+      <c r="C17" s="3" t="inlineStr">
         <is>
           <t>津贴补贴</t>
         </is>
       </c>
-      <c r="D17" s="5" t="inlineStr">
+      <c r="D17" s="3" t="inlineStr">
         <is>
           <t>390元/月</t>
         </is>
       </c>
-      <c r="E17" s="5" t="inlineStr">
+      <c r="E17" s="3" t="inlineStr">
         <is>
           <t>全员</t>
         </is>
       </c>
-      <c r="F17" s="5" t="inlineStr">
+      <c r="F17" s="3" t="inlineStr">
         <is>
           <t>随工资发放</t>
         </is>
       </c>
-      <c r="G17" s="5" t="inlineStr">
+      <c r="G17" s="3" t="inlineStr">
         <is>
           <t>按出勤折算</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="4" t="n">
+      <c r="A18" s="2" t="n">
         <v>17</v>
       </c>
-      <c r="B18" s="5" t="inlineStr">
+      <c r="B18" s="3" t="inlineStr">
         <is>
           <t>通讯补贴</t>
         </is>
       </c>
-      <c r="C18" s="5" t="inlineStr">
+      <c r="C18" s="3" t="inlineStr">
         <is>
           <t>津贴补贴</t>
         </is>
       </c>
-      <c r="D18" s="5" t="inlineStr">
+      <c r="D18" s="3" t="inlineStr">
         <is>
           <t>130元/月</t>
         </is>
       </c>
-      <c r="E18" s="5" t="inlineStr">
+      <c r="E18" s="3" t="inlineStr">
         <is>
           <t>运营/销售岗位</t>
         </is>
       </c>
-      <c r="F18" s="5" t="inlineStr">
+      <c r="F18" s="3" t="inlineStr">
         <is>
           <t>随工资发放</t>
         </is>
       </c>
-      <c r="G18" s="5" t="inlineStr">
+      <c r="G18" s="3" t="inlineStr">
         <is>
           <t>需报销话费发票</t>
         </is>
@@ -3303,14 +3188,14 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="6" t="inlineStr">
-        <is>
-          <t>互联网/电商 · 电商运营助理 · 薪资计算示例</t>
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>互联网/科技 · 互联网电商运营助理 · 薪资计算示例</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="4" t="inlineStr">
+      <c r="A3" s="2" t="inlineStr">
         <is>
           <t>员工姓名</t>
         </is>
@@ -3320,29 +3205,29 @@
           <t>张三</t>
         </is>
       </c>
-      <c r="C3" s="4" t="inlineStr">
+      <c r="C3" s="2" t="inlineStr">
         <is>
           <t>部门</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>互联网/电商事业部</t>
-        </is>
-      </c>
-      <c r="E3" s="4" t="inlineStr">
+          <t>互联网/科技事业部</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
         <is>
           <t>岗位</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>电商运营助理</t>
+          <t>互联网电商运营助理</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="4" t="inlineStr">
+      <c r="A4" s="2" t="inlineStr">
         <is>
           <t>入职日期</t>
         </is>
@@ -3352,7 +3237,7 @@
           <t>2026-03-01</t>
         </is>
       </c>
-      <c r="C4" s="4" t="inlineStr">
+      <c r="C4" s="2" t="inlineStr">
         <is>
           <t>工龄</t>
         </is>
@@ -3362,7 +3247,7 @@
           <t>1年</t>
         </is>
       </c>
-      <c r="E4" s="4" t="inlineStr">
+      <c r="E4" s="2" t="inlineStr">
         <is>
           <t>职级</t>
         </is>
@@ -3374,7 +3259,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="4" t="inlineStr">
+      <c r="A5" s="2" t="inlineStr">
         <is>
           <t>计薪月份</t>
         </is>
@@ -3384,7 +3269,7 @@
           <t>2026-07</t>
         </is>
       </c>
-      <c r="C5" s="4" t="inlineStr">
+      <c r="C5" s="2" t="inlineStr">
         <is>
           <t>应出勤天数</t>
         </is>
@@ -3392,7 +3277,7 @@
       <c r="D5" s="2" t="n">
         <v>21.75</v>
       </c>
-      <c r="E5" s="4" t="inlineStr">
+      <c r="E5" s="2" t="inlineStr">
         <is>
           <t>实际出勤天数</t>
         </is>
@@ -3402,7 +3287,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="4" t="inlineStr">
+      <c r="A6" s="2" t="inlineStr">
         <is>
           <t>基本工资</t>
         </is>
@@ -3410,7 +3295,7 @@
       <c r="B6" s="2" t="n">
         <v>4500</v>
       </c>
-      <c r="C6" s="4" t="inlineStr">
+      <c r="C6" s="2" t="inlineStr">
         <is>
           <t>岗位工资</t>
         </is>
@@ -3418,7 +3303,7 @@
       <c r="D6" s="2" t="n">
         <v>1800</v>
       </c>
-      <c r="E6" s="4" t="inlineStr">
+      <c r="E6" s="2" t="inlineStr">
         <is>
           <t>绩效工资标准</t>
         </is>
@@ -3428,7 +3313,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="4" t="inlineStr">
+      <c r="A7" s="2" t="inlineStr">
         <is>
           <t>全勤奖标准</t>
         </is>
@@ -3436,7 +3321,7 @@
       <c r="B7" s="2" t="n">
         <v>260</v>
       </c>
-      <c r="C7" s="4" t="inlineStr">
+      <c r="C7" s="2" t="inlineStr">
         <is>
           <t>餐补标准</t>
         </is>
@@ -3444,7 +3329,7 @@
       <c r="D7" s="2" t="n">
         <v>390</v>
       </c>
-      <c r="E7" s="4" t="inlineStr">
+      <c r="E7" s="2" t="inlineStr">
         <is>
           <t>交通补贴标准</t>
         </is>
@@ -3454,7 +3339,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="4" t="inlineStr">
+      <c r="A8" s="2" t="inlineStr">
         <is>
           <t>通讯补贴标准</t>
         </is>
@@ -3462,7 +3347,7 @@
       <c r="B8" s="2" t="n">
         <v>130</v>
       </c>
-      <c r="C8" s="4" t="inlineStr">
+      <c r="C8" s="2" t="inlineStr">
         <is>
           <t>五险一金基数</t>
         </is>
@@ -3470,17 +3355,17 @@
       <c r="D8" s="2" t="n">
         <v>6500</v>
       </c>
-      <c r="E8" s="4" t="inlineStr">
+      <c r="E8" s="2" t="inlineStr">
         <is>
           <t>公积金比例</t>
         </is>
       </c>
-      <c r="F8" s="7" t="n">
+      <c r="F8" s="5" t="n">
         <v>0.05</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="4" t="inlineStr">
+      <c r="A9" s="2" t="inlineStr">
         <is>
           <t>城市</t>
         </is>
@@ -3490,7 +3375,7 @@
           <t>广州</t>
         </is>
       </c>
-      <c r="C9" s="4" t="inlineStr">
+      <c r="C9" s="2" t="inlineStr">
         <is>
           <t>城市系数</t>
         </is>
@@ -3498,7 +3383,7 @@
       <c r="D9" s="2" t="n">
         <v>1.3</v>
       </c>
-      <c r="E9" s="4" t="inlineStr"/>
+      <c r="E9" s="2" t="inlineStr"/>
       <c r="F9" s="2" t="inlineStr"/>
     </row>
     <row r="10">
@@ -3517,14 +3402,14 @@
           <t>计算说明</t>
         </is>
       </c>
-      <c r="D10" s="8" t="inlineStr">
+      <c r="D10" s="6" t="inlineStr">
         <is>
           <t>绩效考核示例</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="4" t="inlineStr">
+      <c r="A11" s="2" t="inlineStr">
         <is>
           <t>基本工资</t>
         </is>
@@ -3532,7 +3417,7 @@
       <c r="B11" s="2" t="n">
         <v>4500</v>
       </c>
-      <c r="C11" s="5" t="inlineStr">
+      <c r="C11" s="3" t="inlineStr">
         <is>
           <t>固定</t>
         </is>
@@ -3554,7 +3439,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="4" t="inlineStr">
+      <c r="A12" s="2" t="inlineStr">
         <is>
           <t>岗位工资</t>
         </is>
@@ -3562,52 +3447,52 @@
       <c r="B12" s="2" t="n">
         <v>1800</v>
       </c>
-      <c r="C12" s="5" t="inlineStr">
+      <c r="C12" s="3" t="inlineStr">
         <is>
           <t>固定</t>
         </is>
       </c>
-      <c r="D12" s="4" t="inlineStr">
-        <is>
-          <t>销售额达成率</t>
-        </is>
-      </c>
-      <c r="E12" s="9" t="n">
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>销售额/GMV 达成率</t>
+        </is>
+      </c>
+      <c r="E12" s="5" t="n">
         <v>0.25</v>
       </c>
-      <c r="F12" s="4" t="n">
+      <c r="F12" s="2" t="n">
         <v>85</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="4" t="inlineStr">
+      <c r="A13" s="2" t="inlineStr">
         <is>
           <t>绩效工资</t>
         </is>
       </c>
-      <c r="B13" s="10">
-        <f>MAX(0.6,MIN(1.2,F20/100))*D8</f>
+      <c r="B13" s="2">
+        <f>MAX(0.6,MIN(1.2,F18/100))*D8</f>
         <v/>
       </c>
-      <c r="C13" s="5" t="inlineStr">
+      <c r="C13" s="3" t="inlineStr">
         <is>
           <t>由加权绩效得分驱动</t>
         </is>
       </c>
-      <c r="D13" s="4" t="inlineStr">
-        <is>
-          <t>订单处理效率</t>
-        </is>
-      </c>
-      <c r="E13" s="9" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="F13" s="4" t="n">
-        <v>90</v>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>用户增长/活跃度</t>
+        </is>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="F13" s="2" t="n">
+        <v>88</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="4" t="inlineStr">
+      <c r="A14" s="2" t="inlineStr">
         <is>
           <t>加班工资</t>
         </is>
@@ -3615,25 +3500,25 @@
       <c r="B14" s="2" t="n">
         <v>650</v>
       </c>
-      <c r="C14" s="5" t="inlineStr">
+      <c r="C14" s="3" t="inlineStr">
         <is>
           <t>实际加班/值班</t>
         </is>
       </c>
-      <c r="D14" s="4" t="inlineStr">
-        <is>
-          <t>客户满意度</t>
-        </is>
-      </c>
-      <c r="E14" s="9" t="n">
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>活动执行完成率</t>
+        </is>
+      </c>
+      <c r="E14" s="5" t="n">
         <v>0.15</v>
       </c>
-      <c r="F14" s="4" t="n">
-        <v>88</v>
+      <c r="F14" s="2" t="n">
+        <v>95</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="4" t="inlineStr">
+      <c r="A15" s="2" t="inlineStr">
         <is>
           <t>全勤奖</t>
         </is>
@@ -3641,25 +3526,25 @@
       <c r="B15" s="2" t="n">
         <v>260</v>
       </c>
-      <c r="C15" s="5" t="inlineStr">
+      <c r="C15" s="3" t="inlineStr">
         <is>
           <t>当月无缺勤</t>
         </is>
       </c>
-      <c r="D15" s="4" t="inlineStr">
-        <is>
-          <t>库存准确率</t>
-        </is>
-      </c>
-      <c r="E15" s="9" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="F15" s="4" t="n">
-        <v>95</v>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>内容/商品质量</t>
+        </is>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="F15" s="2" t="n">
+        <v>88</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="4" t="inlineStr">
+      <c r="A16" s="2" t="inlineStr">
         <is>
           <t>餐补</t>
         </is>
@@ -3667,25 +3552,25 @@
       <c r="B16" s="2" t="n">
         <v>376.55</v>
       </c>
-      <c r="C16" s="5" t="inlineStr">
+      <c r="C16" s="3" t="inlineStr">
         <is>
           <t>标准/应出勤*实际出勤</t>
         </is>
       </c>
-      <c r="D16" s="4" t="inlineStr">
-        <is>
-          <t>活动执行完成率</t>
-        </is>
-      </c>
-      <c r="E16" s="9" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="F16" s="4" t="n">
-        <v>100</v>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>数据分析准确率</t>
+        </is>
+      </c>
+      <c r="E16" s="5" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="F16" s="2" t="n">
+        <v>90</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="4" t="inlineStr">
+      <c r="A17" s="2" t="inlineStr">
         <is>
           <t>交通补贴</t>
         </is>
@@ -3693,25 +3578,25 @@
       <c r="B17" s="2" t="n">
         <v>260</v>
       </c>
-      <c r="C17" s="5" t="inlineStr">
+      <c r="C17" s="3" t="inlineStr">
         <is>
           <t>固定</t>
         </is>
       </c>
-      <c r="D17" s="4" t="inlineStr">
-        <is>
-          <t>数据报表准确率</t>
-        </is>
-      </c>
-      <c r="E17" s="9" t="n">
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>渠道拓展与维护</t>
+        </is>
+      </c>
+      <c r="E17" s="5" t="n">
         <v>0.1</v>
       </c>
-      <c r="F17" s="4" t="n">
-        <v>90</v>
+      <c r="F17" s="2" t="n">
+        <v>85</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="4" t="inlineStr">
+      <c r="A18" s="2" t="inlineStr">
         <is>
           <t>通讯补贴</t>
         </is>
@@ -3719,125 +3604,103 @@
       <c r="B18" s="2" t="n">
         <v>130</v>
       </c>
-      <c r="C18" s="5" t="inlineStr">
+      <c r="C18" s="3" t="inlineStr">
         <is>
           <t>固定</t>
         </is>
       </c>
-      <c r="D18" s="4" t="inlineStr">
-        <is>
-          <t>工作态度与协作</t>
-        </is>
-      </c>
-      <c r="E18" s="9" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="F18" s="4" t="n">
-        <v>92</v>
-      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>加权绩效得分</t>
+        </is>
+      </c>
+      <c r="E18" s="5">
+        <f>SUMPRODUCT(E12:E17,F12:F17)</f>
+        <v/>
+      </c>
+      <c r="F18" s="2" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="4" t="inlineStr">
+      <c r="A19" s="2" t="inlineStr">
         <is>
           <t>应发工资</t>
         </is>
       </c>
-      <c r="B19" s="10">
+      <c r="B19" s="2">
         <f>SUM(B11:B18)</f>
         <v/>
       </c>
-      <c r="C19" s="5" t="inlineStr"/>
-      <c r="D19" s="4" t="inlineStr">
-        <is>
-          <t>学习成长</t>
-        </is>
-      </c>
-      <c r="E19" s="9" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="F19" s="4" t="n">
-        <v>85</v>
-      </c>
+      <c r="C19" s="3" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" s="4" t="inlineStr">
+      <c r="A20" s="2" t="inlineStr">
         <is>
           <t>五险一金(个人)</t>
         </is>
       </c>
-      <c r="B20" s="10">
+      <c r="B20" s="2">
         <f>D8*(8%+2%+0.5%)+D8*F8</f>
         <v/>
       </c>
-      <c r="C20" s="5" t="inlineStr">
+      <c r="C20" s="3" t="inlineStr">
         <is>
           <t>养老+医疗+失业+公积金</t>
         </is>
       </c>
-      <c r="D20" s="4" t="inlineStr">
-        <is>
-          <t>加权绩效得分</t>
-        </is>
-      </c>
-      <c r="E20" s="11">
-        <f>SUMPRODUCT(E12:E19,F12:F19)</f>
-        <v/>
-      </c>
-      <c r="F20" s="4" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" s="4" t="inlineStr">
+      <c r="A21" s="2" t="inlineStr">
         <is>
           <t>个税起征点</t>
         </is>
       </c>
-      <c r="B21" s="4" t="n">
+      <c r="B21" s="2" t="n">
         <v>5000</v>
       </c>
-      <c r="C21" s="5" t="inlineStr"/>
+      <c r="C21" s="3" t="inlineStr"/>
     </row>
     <row r="22">
-      <c r="A22" s="4" t="inlineStr">
+      <c r="A22" s="2" t="inlineStr">
         <is>
           <t>应纳税所得额</t>
         </is>
       </c>
-      <c r="B22" s="10">
+      <c r="B22" s="2">
         <f>MAX(B19-B20-B21,0)</f>
         <v/>
       </c>
-      <c r="C22" s="5" t="inlineStr"/>
+      <c r="C22" s="3" t="inlineStr"/>
     </row>
     <row r="23">
-      <c r="A23" s="4" t="inlineStr">
+      <c r="A23" s="2" t="inlineStr">
         <is>
           <t>个人所得税</t>
         </is>
       </c>
-      <c r="B23" s="10">
+      <c r="B23" s="2">
         <f>IF(B22&lt;=0,0,IF(B22&lt;=3000,B22*3%,IF(B22&lt;=12000,B22*10%-210,IF(B22&lt;=25000,B22*20%-1410,B22*25%-2660))))</f>
         <v/>
       </c>
-      <c r="C23" s="5" t="inlineStr">
+      <c r="C23" s="3" t="inlineStr">
         <is>
           <t>累计预扣法（简化）</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="4" t="inlineStr">
+      <c r="A24" s="2" t="inlineStr">
         <is>
           <t>实发工资</t>
         </is>
       </c>
-      <c r="B24" s="10">
+      <c r="B24" s="2">
         <f>B19-B20-B23</f>
         <v/>
       </c>
-      <c r="C24" s="5" t="inlineStr"/>
+      <c r="C24" s="3" t="inlineStr"/>
     </row>
     <row r="26">
-      <c r="A26" s="8" t="inlineStr">
+      <c r="A26" s="6" t="inlineStr">
         <is>
           <t>奖金计算示例</t>
         </is>
@@ -3861,80 +3724,80 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="4" t="inlineStr">
+      <c r="A28" s="2" t="inlineStr">
         <is>
           <t>月度销售提成</t>
         </is>
       </c>
-      <c r="B28" s="4" t="n">
+      <c r="B28" s="2" t="n">
         <v>800</v>
       </c>
-      <c r="C28" s="4" t="inlineStr">
+      <c r="C28" s="2" t="inlineStr">
         <is>
           <t>按实际业绩计提</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="4" t="inlineStr">
+      <c r="A29" s="2" t="inlineStr">
         <is>
           <t>月度绩效奖金</t>
         </is>
       </c>
-      <c r="B29" s="10">
+      <c r="B29" s="2">
         <f>B13</f>
         <v/>
       </c>
-      <c r="C29" s="4" t="inlineStr">
+      <c r="C29" s="2" t="inlineStr">
         <is>
           <t>绩效工资联动</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="4" t="inlineStr">
+      <c r="A30" s="2" t="inlineStr">
         <is>
           <t>全勤奖</t>
         </is>
       </c>
-      <c r="B30" s="4" t="n">
+      <c r="B30" s="2" t="n">
         <v>260</v>
       </c>
-      <c r="C30" s="4" t="inlineStr">
+      <c r="C30" s="2" t="inlineStr">
         <is>
           <t>当月无缺勤</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="4" t="inlineStr">
+      <c r="A31" s="2" t="inlineStr">
         <is>
           <t>季度奖金(预估)</t>
         </is>
       </c>
-      <c r="B31" s="4" t="n">
+      <c r="B31" s="2" t="n">
         <v>2250</v>
       </c>
-      <c r="C31" s="4" t="inlineStr">
+      <c r="C31" s="2" t="inlineStr">
         <is>
           <t>基本工资*系数</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="4" t="inlineStr">
+      <c r="A32" s="2" t="inlineStr">
         <is>
           <t>奖金合计</t>
         </is>
       </c>
-      <c r="B32" s="10">
+      <c r="B32" s="2">
         <f>SUM(B28:B31)</f>
         <v/>
       </c>
-      <c r="C32" s="4" t="inlineStr"/>
+      <c r="C32" s="2" t="inlineStr"/>
     </row>
     <row r="33">
-      <c r="E33" s="8" t="inlineStr">
+      <c r="E33" s="6" t="inlineStr">
         <is>
           <t>全年薪酬总包预估</t>
         </is>
@@ -3953,64 +3816,64 @@
       </c>
     </row>
     <row r="35">
-      <c r="E35" s="4" t="inlineStr">
+      <c r="E35" s="2" t="inlineStr">
         <is>
           <t>年固定薪资</t>
         </is>
       </c>
-      <c r="F35" s="10">
+      <c r="F35" s="2">
         <f>B19*12</f>
         <v/>
       </c>
-      <c r="G35" s="4" t="inlineStr"/>
+      <c r="G35" s="2" t="inlineStr"/>
     </row>
     <row r="36">
-      <c r="E36" s="4" t="inlineStr">
+      <c r="E36" s="2" t="inlineStr">
         <is>
           <t>年浮动奖金(提成+绩效)</t>
         </is>
       </c>
-      <c r="F36" s="10">
+      <c r="F36" s="2">
         <f>(B28+B29)*12</f>
         <v/>
       </c>
-      <c r="G36" s="4" t="inlineStr"/>
+      <c r="G36" s="2" t="inlineStr"/>
     </row>
     <row r="37">
-      <c r="E37" s="4" t="inlineStr">
+      <c r="E37" s="2" t="inlineStr">
         <is>
           <t>年终奖(1个月)</t>
         </is>
       </c>
-      <c r="F37" s="10">
+      <c r="F37" s="2">
         <f>B11+B12</f>
         <v/>
       </c>
-      <c r="G37" s="4" t="inlineStr"/>
+      <c r="G37" s="2" t="inlineStr"/>
     </row>
     <row r="38">
-      <c r="E38" s="4" t="inlineStr">
+      <c r="E38" s="2" t="inlineStr">
         <is>
           <t>年福利(餐补+交通+通讯+节日)</t>
         </is>
       </c>
-      <c r="F38" s="10">
+      <c r="F38" s="2">
         <f>(B16+B17+B18+B30)*12+1200</f>
         <v/>
       </c>
-      <c r="G38" s="4" t="inlineStr"/>
+      <c r="G38" s="2" t="inlineStr"/>
     </row>
     <row r="39">
-      <c r="E39" s="4" t="inlineStr">
+      <c r="E39" s="2" t="inlineStr">
         <is>
           <t>全年总现金收入</t>
         </is>
       </c>
-      <c r="F39" s="10">
+      <c r="F39" s="2">
         <f>F35+F36+F37+F38</f>
         <v/>
       </c>
-      <c r="G39" s="4" t="inlineStr"/>
+      <c r="G39" s="2" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -4018,7 +3881,7 @@
           <t>合规状态</t>
         </is>
       </c>
-      <c r="B40" s="12">
+      <c r="B40" s="7">
         <f>COUNTIF(合规校验!F:F,"PASS")&amp;"项通过/"&amp;COUNTA(合规校验!F:F)-1&amp;"项校验"</f>
         <v/>
       </c>
@@ -4091,212 +3954,212 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="4" t="n">
+      <c r="A2" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="B2" s="4" t="inlineStr">
+      <c r="B2" s="2" t="inlineStr">
         <is>
           <t>最低工资合规</t>
         </is>
       </c>
-      <c r="C2" s="4" t="inlineStr">
+      <c r="C2" s="2" t="inlineStr">
         <is>
           <t>基本工资 ≥ 2300元</t>
         </is>
       </c>
-      <c r="D2" s="4" t="n">
+      <c r="D2" s="2" t="n">
         <v>4500</v>
       </c>
-      <c r="E2" s="4" t="n">
+      <c r="E2" s="2" t="n">
         <v>2300</v>
       </c>
-      <c r="F2" s="10">
+      <c r="F2" s="2">
         <f>IF(D2&gt;=E2,"PASS","BLOCK")</f>
         <v/>
       </c>
-      <c r="G2" s="4" t="inlineStr">
+      <c r="G2" s="2" t="inlineStr">
         <is>
           <t>低于最低工资为严重违规</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="4" t="n">
+      <c r="A3" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="B3" s="4" t="inlineStr">
+      <c r="B3" s="2" t="inlineStr">
         <is>
           <t>社保基数下限</t>
         </is>
       </c>
-      <c r="C3" s="4" t="inlineStr">
+      <c r="C3" s="2" t="inlineStr">
         <is>
           <t>社保基数 ≥ 5284元</t>
         </is>
       </c>
-      <c r="D3" s="4" t="n">
+      <c r="D3" s="2" t="n">
         <v>6500</v>
       </c>
-      <c r="E3" s="4" t="n">
+      <c r="E3" s="2" t="n">
         <v>5284</v>
       </c>
-      <c r="F3" s="10">
+      <c r="F3" s="2">
         <f>IF(D3&gt;=E3,"PASS","WARN")</f>
         <v/>
       </c>
-      <c r="G3" s="4" t="inlineStr">
+      <c r="G3" s="2" t="inlineStr">
         <is>
           <t>低于下限需按最低基数缴纳</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="4" t="n">
+      <c r="A4" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="B4" s="4" t="inlineStr">
+      <c r="B4" s="2" t="inlineStr">
         <is>
           <t>社保基数上限</t>
         </is>
       </c>
-      <c r="C4" s="4" t="inlineStr">
+      <c r="C4" s="2" t="inlineStr">
         <is>
           <t>社保基数 ≤ 26421元</t>
         </is>
       </c>
-      <c r="D4" s="4" t="n">
+      <c r="D4" s="2" t="n">
         <v>6500</v>
       </c>
-      <c r="E4" s="4" t="n">
+      <c r="E4" s="2" t="n">
         <v>26421</v>
       </c>
-      <c r="F4" s="10">
+      <c r="F4" s="2">
         <f>IF(D4&lt;=E4,"PASS","WARN")</f>
         <v/>
       </c>
-      <c r="G4" s="4" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>超过上限按上限缴纳</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="4" t="n">
+      <c r="A5" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="B5" s="4" t="inlineStr">
+      <c r="B5" s="2" t="inlineStr">
         <is>
           <t>公积金比例合规</t>
         </is>
       </c>
-      <c r="C5" s="4" t="inlineStr">
+      <c r="C5" s="2" t="inlineStr">
         <is>
           <t>比例在 5%-12% 之间</t>
         </is>
       </c>
-      <c r="D5" s="4" t="n">
+      <c r="D5" s="2" t="n">
         <v>0.05</v>
       </c>
-      <c r="E5" s="9" t="n">
+      <c r="E5" s="5" t="n">
         <v>0.05</v>
       </c>
-      <c r="F5" s="10">
+      <c r="F5" s="2">
         <f>IF(AND(D5&gt;=E5,D5&lt;=0.12),"PASS","WARN")</f>
         <v/>
       </c>
-      <c r="G5" s="4" t="inlineStr">
+      <c r="G5" s="2" t="inlineStr">
         <is>
           <t>比例需符合当地政策</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="4" t="n">
+      <c r="A6" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="B6" s="4" t="inlineStr">
+      <c r="B6" s="2" t="inlineStr">
         <is>
           <t>绩效工资占比</t>
         </is>
       </c>
-      <c r="C6" s="4" t="inlineStr">
+      <c r="C6" s="2" t="inlineStr">
         <is>
           <t>绩效工资 ≤ 固定薪酬*50%</t>
         </is>
       </c>
-      <c r="D6" s="4" t="n">
+      <c r="D6" s="2" t="n">
         <v>2000</v>
       </c>
-      <c r="E6" s="4" t="n">
+      <c r="E6" s="2" t="n">
         <v>3150</v>
       </c>
-      <c r="F6" s="10">
+      <c r="F6" s="2">
         <f>IF(D6&lt;=E6,"PASS","WARN")</f>
         <v/>
       </c>
-      <c r="G6" s="4" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>占比过高影响收入稳定性</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="4" t="n">
+      <c r="A7" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="B7" s="4" t="inlineStr">
+      <c r="B7" s="2" t="inlineStr">
         <is>
           <t>个税合规</t>
         </is>
       </c>
-      <c r="C7" s="4" t="inlineStr">
+      <c r="C7" s="2" t="inlineStr">
         <is>
           <t>应纳税所得额 ≥ 0</t>
         </is>
       </c>
-      <c r="D7" s="10">
+      <c r="D7" s="2">
         <f>'计算示例'!B22</f>
         <v/>
       </c>
-      <c r="E7" s="4" t="n">
+      <c r="E7" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="F7" s="10">
+      <c r="F7" s="2">
         <f>IF(D7&gt;=E7,"PASS","WARN")</f>
         <v/>
       </c>
-      <c r="G7" s="4" t="inlineStr">
+      <c r="G7" s="2" t="inlineStr">
         <is>
           <t>应纳税所得额为负需检查</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="4" t="n">
+      <c r="A8" s="2" t="n">
         <v>7</v>
       </c>
-      <c r="B8" s="4" t="inlineStr">
+      <c r="B8" s="2" t="inlineStr">
         <is>
           <t>实发工资为正</t>
         </is>
       </c>
-      <c r="C8" s="4" t="inlineStr">
+      <c r="C8" s="2" t="inlineStr">
         <is>
           <t>实发工资 &gt; 0</t>
         </is>
       </c>
-      <c r="D8" s="10">
+      <c r="D8" s="2">
         <f>'计算示例'!B24</f>
         <v/>
       </c>
-      <c r="E8" s="4" t="n">
+      <c r="E8" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="F8" s="10">
+      <c r="F8" s="2">
         <f>IF(D8&gt;0,"PASS","BLOCK")</f>
         <v/>
       </c>
-      <c r="G8" s="4" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>实发工资必须为正</t>
         </is>
@@ -4339,119 +4202,119 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="5" t="inlineStr">
+      <c r="A2" s="3" t="inlineStr">
         <is>
           <t>&lt; 60</t>
         </is>
       </c>
-      <c r="B2" s="5" t="inlineStr">
+      <c r="B2" s="3" t="inlineStr">
         <is>
           <t>0.6</t>
         </is>
       </c>
-      <c r="C2" s="5" t="inlineStr">
+      <c r="C2" s="3" t="inlineStr">
         <is>
           <t>不合格，绩效奖金打折</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="5" t="inlineStr">
+      <c r="A3" s="3" t="inlineStr">
         <is>
           <t>60 - 70</t>
         </is>
       </c>
-      <c r="B3" s="5" t="inlineStr">
+      <c r="B3" s="3" t="inlineStr">
         <is>
           <t>0.7</t>
         </is>
       </c>
-      <c r="C3" s="5" t="inlineStr">
+      <c r="C3" s="3" t="inlineStr">
         <is>
           <t>待改进</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="5" t="inlineStr">
+      <c r="A4" s="3" t="inlineStr">
         <is>
           <t>70 - 80</t>
         </is>
       </c>
-      <c r="B4" s="5" t="inlineStr">
+      <c r="B4" s="3" t="inlineStr">
         <is>
           <t>0.8</t>
         </is>
       </c>
-      <c r="C4" s="5" t="inlineStr">
+      <c r="C4" s="3" t="inlineStr">
         <is>
           <t>合格</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="5" t="inlineStr">
+      <c r="A5" s="3" t="inlineStr">
         <is>
           <t>80 - 90</t>
         </is>
       </c>
-      <c r="B5" s="5" t="inlineStr">
+      <c r="B5" s="3" t="inlineStr">
         <is>
           <t>0.9</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr">
+      <c r="C5" s="3" t="inlineStr">
         <is>
           <t>良好</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="5" t="inlineStr">
+      <c r="A6" s="3" t="inlineStr">
         <is>
           <t>90 - 100</t>
         </is>
       </c>
-      <c r="B6" s="5" t="inlineStr">
+      <c r="B6" s="3" t="inlineStr">
         <is>
           <t>1.0</t>
         </is>
       </c>
-      <c r="C6" s="5" t="inlineStr">
+      <c r="C6" s="3" t="inlineStr">
         <is>
           <t>达标</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="5" t="inlineStr">
+      <c r="A7" s="3" t="inlineStr">
         <is>
           <t>100 - 110</t>
         </is>
       </c>
-      <c r="B7" s="5" t="inlineStr">
+      <c r="B7" s="3" t="inlineStr">
         <is>
           <t>1.1</t>
         </is>
       </c>
-      <c r="C7" s="5" t="inlineStr">
+      <c r="C7" s="3" t="inlineStr">
         <is>
           <t>优秀</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="5" t="inlineStr">
+      <c r="A8" s="3" t="inlineStr">
         <is>
           <t>&gt;= 110</t>
         </is>
       </c>
-      <c r="B8" s="5" t="inlineStr">
+      <c r="B8" s="3" t="inlineStr">
         <is>
           <t>1.2</t>
         </is>
       </c>
-      <c r="C8" s="5" t="inlineStr">
+      <c r="C8" s="3" t="inlineStr">
         <is>
           <t>卓越</t>
         </is>
